--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억   ·   현금 199억(4.3%)      오늘 2026-10-19  vs  5일전 2026-10-12      매수 13종목  /  매도 26종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 13종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1543,23 +1543,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-376976491</v>
+        <v>-1047982754</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.08%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>
@@ -1571,30 +1571,30 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1047982754</v>
+        <v>-376976491</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.08%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억   ·   현금 59억(1.9%)      오늘 2026-10-19  vs  5일전 2026-10-12      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억   ·   현금 40억(1.7%)      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2264,7 +2264,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억   ·   현금 47억(2.4%)      오늘 2026-10-19  vs  5일전 2026-10-12      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억   ·   현금 3억(1.3%)      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 13종목  /  매도 26종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,651억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 13종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>489</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4366238047</v>
+        <v>4366234963</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-310</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2887774699</v>
+        <v>-2887772660</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>139</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>487631578</v>
+        <v>487631234</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-126</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1969137297</v>
+        <v>-1969135906</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>744201540</v>
+        <v>744201015</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-103</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1864874162</v>
+        <v>-1864872844</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>893882216</v>
+        <v>893881585</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-79</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2113803512</v>
+        <v>-2113802019</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3372373817</v>
+        <v>3372371435</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-74</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3967370361</v>
+        <v>-3967367558</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1400877939</v>
+        <v>1400876950</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-73</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1786872533</v>
+        <v>-1786871271</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>36</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1580447183</v>
+        <v>1580446066</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-71</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2891837800</v>
+        <v>-2891835758</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1328733122</v>
+        <v>1328732183</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-46</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-663732321</v>
+        <v>-663731852</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>863309859</v>
+        <v>1333092581</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>3.40%→3.62%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>-35</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-934760976</v>
+        <v>-934760316</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1333093523</v>
+        <v>863309249</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.62%</t>
+          <t>1.01%→1.17%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>-29</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2281877153</v>
+        <v>-2281875541</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1068298259</v>
+        <v>1068297504</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-26</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1473815557</v>
+        <v>-1473814516</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1652988400</v>
+        <v>1652987233</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-23</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-943630429</v>
+        <v>-943629762</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1290777813</v>
+        <v>1290776901</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-21</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-814750847</v>
+        <v>-814750272</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>-20</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-975144236</v>
+        <v>-975143547</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1881909456</v>
+        <v>-1881908126</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>-14</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1288894912</v>
+        <v>-1288894002</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-500058721</v>
+        <v>-500058368</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>-11</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-886251515</v>
+        <v>-886250889</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>-9</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1434175547</v>
+        <v>-1434174534</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-822728399</v>
+        <v>-822727818</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-418301201</v>
+        <v>-418300906</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1251633303</v>
+        <v>-1251632419</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-911720221</v>
+        <v>-911719577</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1179290286</v>
+        <v>-1179289453</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1047982754</v>
+        <v>-1047982014</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-376976491</v>
+        <v>-376976225</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,080억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1690,7 +1690,7 @@
         <v>56</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1552264644</v>
+        <v>1558122010</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>-90</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-612468254</v>
+        <v>-614779362</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>51</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>841984850</v>
+        <v>845162022</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2946801223</v>
+        <v>-2957920778</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>39</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>871240862</v>
+        <v>874528430</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>-19</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-919391382</v>
+        <v>-922860643</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>597363248</v>
+        <v>599617358</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>-17</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1747940726</v>
+        <v>-1754536462</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>12</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>623280259</v>
+        <v>625632165</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>-14</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2949451224</v>
+        <v>-2960580779</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>620100257</v>
+        <v>622440164</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>261184108</v>
+        <v>262169669</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,391억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2055,7 +2055,7 @@
         <v>36</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1677110502</v>
+        <v>1682208000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-150</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-4086180248</v>
+        <v>-4098600000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>25</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>3273550199</v>
+        <v>3283500000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>-39</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-2514876153</v>
+        <v>-2522520000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>21</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2908689177</v>
+        <v>2917530000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>-30</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-519162032</v>
+        <v>-520740000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>-25</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-583152535</v>
+        <v>-584925000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>-20</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-902776055</v>
+        <v>-905520000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>-6</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1097544067</v>
+        <v>-1100880000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 5종목  /  매도 10종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,004억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 5종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2360,7 +2360,7 @@
         <v>229</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>17015150892</v>
+        <v>17148437777</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>-356</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-4247238426</v>
+        <v>-4280508844</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>125</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1809674244</v>
+        <v>1823850189</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>-313</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-2967004011</v>
+        <v>-2990245810</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>926323413</v>
+        <v>933579697</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>-242</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-9083224205</v>
+        <v>-9154376949</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>53</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>879961282</v>
+        <v>886854392</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>-238</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-2014502558</v>
+        <v>-2030283010</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>7457006885</v>
+        <v>7515420779</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>-235</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-2128617361</v>
+        <v>-2145291722</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>-63</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-1017036925</v>
+        <v>-1025003806</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>-56</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-1958201582</v>
+        <v>-1973541005</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>-34</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-5176242838</v>
+        <v>-5216790541</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>-20</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1792439251</v>
+        <v>-1806480187</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>-12</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-110303954</v>
+        <v>-111168012</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 276억      오늘 2026-10-19  vs  5일전 2026-10-12      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
@@ -2809,11 +2809,11 @@
         <v>17</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>53191268</v>
+        <v>56038817</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.53%</t>
+          <t>2.34%→2.54%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2830,11 +2830,11 @@
         <v>-88</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-58901005</v>
+        <v>-55481377</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>8.10%→7.87%</t>
+          <t>7.29%→7.08%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2853,11 +2853,11 @@
         <v>8</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>66088761</v>
+        <v>67964820</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.45%</t>
+          <t>2.16%→2.40%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -2874,11 +2874,11 @@
         <v>-31</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-49224871</v>
+        <v>-48601815</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>2.93%→2.74%</t>
+          <t>2.77%→2.59%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2897,11 +2897,11 @@
         <v>6</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>59294965</v>
+        <v>64641619</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.48%</t>
+          <t>1.31%→1.54%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2918,11 +2918,11 @@
         <v>-8</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-64641561</v>
+        <v>-61372018</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.39%</t>
+          <t>2.40%→2.17%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1333092581</v>
+        <v>863309249</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.62%</t>
+          <t>1.01%→1.17%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>863309249</v>
+        <v>1333092581</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>3.40%→3.62%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1487,23 +1487,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-911719577</v>
+        <v>-1179289453</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.71%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1515,23 +1515,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1179289453</v>
+        <v>-911719577</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.71%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>863309249</v>
+        <v>1333092581</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>3.40%→3.62%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1333092581</v>
+        <v>863309249</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.62%</t>
+          <t>1.01%→1.17%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1403,23 +1403,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-822727818</v>
+        <v>-418300906</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.28%→1.16%</t>
+          <t>0.34%→0.24%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1431,23 +1431,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-418300906</v>
+        <v>-822727818</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.24%</t>
+          <t>1.28%→1.16%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1543,23 +1543,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1047982014</v>
+        <v>-376976225</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.16%</t>
+          <t>5.50%→5.08%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>5→2</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1571,23 +1571,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-376976225</v>
+        <v>-1047982014</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>5.50%→5.08%</t>
+          <t>0.39%→0.16%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>5→2</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1333092581</v>
+        <v>863309249</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.62%</t>
+          <t>1.01%→1.17%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>863309249</v>
+        <v>1333092581</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>3.40%→3.62%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1487,23 +1487,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1179289453</v>
+        <v>-911719577</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.71%</t>
+          <t>0.98%→0.72%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1515,23 +1515,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-911719577</v>
+        <v>-1179289453</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.72%</t>
+          <t>2.56%→2.71%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261019.xlsx
+++ b/reports/pdf_rolling5_20261019.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>GST</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>863309249</v>
+        <v>1333092581</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>3.40%→3.62%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>96→115</t>
+          <t>211→230</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>19</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1333092581</v>
+        <v>863309249</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>3.40%→3.62%</t>
+          <t>1.01%→1.17%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>211→230</t>
+          <t>96→115</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
